--- a/output/pdf_financials_xlsx/CDA.xlsx
+++ b/output/pdf_financials_xlsx/CDA.xlsx
@@ -1346,19 +1346,19 @@
         <v>-2.136495</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>6.35831</v>
+        <v>-6.35831</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>1.740169</v>
+        <v>-1.740169</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1.753039</v>
+        <v>-1.753039</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1.042206</v>
+        <v>-1.042206</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>9.441107000000001</v>
+        <v>-9.441107000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1662,19 +1662,19 @@
         <v>-2.136495</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>6.35831</v>
+        <v>-6.35831</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>1.740169</v>
+        <v>-1.740169</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>1.753039</v>
+        <v>-1.753039</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>1.042206</v>
+        <v>-1.042206</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>9.441107000000001</v>
+        <v>-9.441107000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1845,19 +1845,19 @@
         <v>-2.136495</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>6.35831</v>
+        <v>-6.35831</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1.740169</v>
+        <v>-1.740169</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>1.753039</v>
+        <v>-1.753039</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>1.042206</v>
+        <v>-1.042206</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>9.441107000000001</v>
+        <v>-9.441107000000001</v>
       </c>
     </row>
     <row r="24">
@@ -2159,19 +2159,19 @@
         <v>-2.136495</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>6.35831</v>
+        <v>-6.35831</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>1.740169</v>
+        <v>-1.740169</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>1.753039</v>
+        <v>-1.753039</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>1.042206</v>
+        <v>-1.042206</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>9.441107000000001</v>
+        <v>-9.441107000000001</v>
       </c>
     </row>
     <row r="28">
@@ -2281,19 +2281,19 @@
         <v>-2.116539</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>6.369988</v>
+        <v>-6.346632</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.740169</v>
+        <v>-1.740169</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>1.753039</v>
+        <v>-1.753039</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>1.042206</v>
+        <v>-1.042206</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>9.441107000000001</v>
+        <v>-9.441107000000001</v>
       </c>
     </row>
     <row r="30">
@@ -2344,19 +2344,19 @@
         <v>-2711.147973561511</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>3565.584488278888</v>
+        <v>-3552.511027024607</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>580.6931601656484</v>
+        <v>-580.6931601656484</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>1078.22923393917</v>
+        <v>-1078.22923393917</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>1168.248310185964</v>
+        <v>-1168.248310185964</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>7496.273740710157</v>
+        <v>-7496.273740710157</v>
       </c>
     </row>
     <row r="31">
@@ -2405,19 +2405,19 @@
         <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -2468,19 +2468,19 @@
         <v>-2736.71030383768</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>3559.047757651747</v>
+        <v>-3559.047757651747</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>580.6931601656484</v>
+        <v>-580.6931601656484</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>1078.22923393917</v>
+        <v>-1078.22923393917</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>1168.248310185964</v>
+        <v>-1168.248310185964</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>7496.273740710157</v>
+        <v>-7496.273740710157</v>
       </c>
     </row>
     <row r="33">
@@ -6099,7 +6099,7 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>0.101541</v>
       </c>
       <c r="J91" s="3" t="n">
         <v>0.005107</v>
@@ -6148,7 +6148,7 @@
         <v>0.132282</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0.5093800000000001</v>
+        <v>1.892104</v>
       </c>
       <c r="F92" s="3" t="n">
         <v>1.572821</v>
@@ -15922,7 +15922,11 @@
           <t>Cumulative translation reserve</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -22858,7 +22862,11 @@
           <t>Share based payment reserves (Note 14)</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -49081,19 +49089,19 @@
         </is>
       </c>
       <c r="R385" s="5" t="n">
-        <v>6.35831</v>
+        <v>-6.35831</v>
       </c>
       <c r="S385" s="5" t="n">
-        <v>1.740169</v>
+        <v>-1.740169</v>
       </c>
       <c r="T385" s="5" t="n">
-        <v>1.753039</v>
+        <v>-1.753039</v>
       </c>
       <c r="U385" s="5" t="n">
-        <v>1.042206</v>
+        <v>-1.042206</v>
       </c>
       <c r="V385" s="5" t="n">
-        <v>9.441107000000001</v>
+        <v>-9.441107000000001</v>
       </c>
     </row>
     <row r="386">
@@ -49467,19 +49475,19 @@
         <v>-2.185111</v>
       </c>
       <c r="R389" s="5" t="n">
-        <v>6.387585</v>
+        <v>-6.387585</v>
       </c>
       <c r="S389" s="5" t="n">
-        <v>1.70023</v>
+        <v>-1.70023</v>
       </c>
       <c r="T389" s="5" t="n">
-        <v>1.752321</v>
+        <v>-1.752321</v>
       </c>
       <c r="U389" s="5" t="n">
-        <v>0.932845</v>
+        <v>-0.932845</v>
       </c>
       <c r="V389" s="5" t="n">
-        <v>9.433157</v>
+        <v>-9.433157</v>
       </c>
     </row>
     <row r="390">
@@ -50373,10 +50381,10 @@
         </is>
       </c>
       <c r="T398" s="5" t="n">
-        <v>1.752321</v>
+        <v>-1.752321</v>
       </c>
       <c r="U398" s="5" t="n">
-        <v>1.151567</v>
+        <v>-1.151567</v>
       </c>
       <c r="V398" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CDA.xlsx
+++ b/output/pdf_financials_xlsx/CDA.xlsx
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.023664</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.015043</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001127</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -2120,13 +2120,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.62108</v>
+        <v>-0.644744</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.830763</v>
+        <v>-0.8458059999999999</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.114599</v>
+        <v>-2.115726</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-9.369216</v>
@@ -2242,13 +2242,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.62108</v>
+        <v>-0.644744</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.830763</v>
+        <v>-0.8458059999999999</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.114599</v>
+        <v>-2.115726</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-9.369216</v>
@@ -2303,10 +2303,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-357.8866089281495</v>
+        <v>-371.5225796785774</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-4387.678250765818</v>
+        <v>-4467.127918031055</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.028271</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.077297</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>1.63837</v>
@@ -2512,43 +2512,43 @@
         <v>0.085581</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.063038</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.011739</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.041072</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.138168</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.221923</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.65844</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.219228</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.803086</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.305374</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.119311</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.887305</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.125503</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>2.844774</v>
       </c>
     </row>
     <row r="35">
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.028271</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.077297</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>1.63837</v>
@@ -2634,43 +2634,43 @@
         <v>0.085581</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.063038</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.011739</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.041072</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.138168</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.221923</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.65844</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.219228</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.803086</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>1.305374</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.119311</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.887305</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.125503</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>2.844774</v>
       </c>
     </row>
     <row r="37">
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.512923</v>
+        <v>0.484652</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.653135</v>
+        <v>1.575838</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.014765</v>
@@ -3366,43 +3366,43 @@
         <v>0.01321</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.074684</v>
+        <v>0.011646</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.029604</v>
+        <v>0.017865</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.048359</v>
+        <v>0.007287</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.149386</v>
+        <v>0.011218</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.316501</v>
+        <v>0.094578</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.803207</v>
+        <v>0.144767</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.265222</v>
+        <v>0.045994</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.190589</v>
+        <v>0.387503</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.432059</v>
+        <v>0.126685</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.145131</v>
+        <v>0.02582</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>1.534563</v>
+        <v>0.647258</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.60073</v>
+        <v>0.475227</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>3.75982</v>
+        <v>0.915046</v>
       </c>
     </row>
     <row r="49">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -13190,7 +13190,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -16244,7 +16244,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
@@ -20840,7 +20840,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -50720,7 +50720,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -55798,7 +55798,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -70542,7 +70542,7 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E591" s="5" t="n">

--- a/output/pdf_financials_xlsx/CDA.xlsx
+++ b/output/pdf_financials_xlsx/CDA.xlsx
@@ -2872,10 +2872,10 @@
         <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.030486</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.040536</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
         <v>0.014033</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.094828</v>
+        <v>0.135364</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>0.074242</v>
@@ -3363,7 +3363,7 @@
         <v>0.071988</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.01321</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.011646</v>
@@ -4390,7 +4390,7 @@
         <v>0.327716</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.284569</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>0</v>
@@ -4567,13 +4567,13 @@
         <v>0.239856</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.057083</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>0</v>
@@ -4628,7 +4628,7 @@
         <v>0.279158</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.343408</v>
+        <v>0.374408</v>
       </c>
       <c r="F68" s="3" t="n">
         <v>0.327716</v>
@@ -7236,7 +7236,7 @@
         <v>0</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.007106</v>
       </c>
       <c r="P110" s="3" t="n">
         <v>0</v>
@@ -7294,7 +7294,7 @@
         <v>0</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001408</v>
       </c>
       <c r="O111" s="3" t="n">
         <v>0</v>
@@ -8737,7 +8737,7 @@
         <v>0</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001408</v>
       </c>
       <c r="O134" s="3" t="n">
         <v>0</v>
@@ -8798,7 +8798,7 @@
         <v>-0.408996</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-2.594128</v>
+        <v>-2.595536</v>
       </c>
       <c r="O135" s="3" t="n">
         <v>-4.177963</v>
@@ -27296,7 +27296,11 @@
           <t>Private placements (note 10) $</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -28724,7 +28728,11 @@
           <t>Private placements</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -29236,7 +29244,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -30484,7 +30496,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -30590,7 +30606,11 @@
           <t>Private placements (note 10)</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -33128,7 +33148,11 @@
           <t>Private placements ,</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
